--- a/src/config/midas_config_values.xlsx
+++ b/src/config/midas_config_values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Documents/code/midas-alt/src/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6040D5E-74C9-2146-8F41-1F957A458D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A686F8-D7E1-044E-A52B-BC3A87515DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="51200" windowHeight="28300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="29320" windowWidth="51200" windowHeight="28300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -20221,7 +20221,7 @@
     <col min="1" max="1" width="58" style="24" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="129.5" style="29" customWidth="1"/>
     <col min="3" max="3" width="50.83203125" style="39" customWidth="1"/>
-    <col min="4" max="4" width="170.6640625" style="24" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="62.5" style="24" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" style="24" customWidth="1"/>
     <col min="6" max="16384" width="10.83203125" style="24"/>
   </cols>
